--- a/research/SFM/Reports/SFM_DCF_Model.xlsx
+++ b/research/SFM/Reports/SFM_DCF_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="201">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -44,117 +44,117 @@
     <t xml:space="preserve">Valuation date</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price as of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30T20:00:01Z regular close (Yahoo Finance chart API); Friday close, two days after the Q3 release and guidance cut, not an after-hours print</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sheet date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">owner_fcf_dcf_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency (model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency (quote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">millions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dcf_engine v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30T22:01:25Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drivers file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFM_Drivers.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percents stored as percents; formulas divide by 100. Blue = input, green = link, black = formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary: Value Sprouts as a self-funded store-growth compounder whose comps have gone negative and whose margin is being reinvested in price, not as the +7% comp business of FY2025 and not as a broken retailer. The owner-FCF build charges SBC (~$25m, 0.3% of sales) in the flows and holds the share count flat; buybacks ($472m in FY2025, ~$330m in FY2026 to date) are how the count stays flat, not a source of value. FY2026 is the guided year (53 weeks, comps -1.7%, EBIT ~$605m, EPS ~$4.80, capex up on a completed distribution centre); FY2027 is management's 'above 5%' EBIT-margin year with the 53rd week lapped; after that growth is new-store arithmetic on a 500-store base fading from ~5.5% to 3%, margins rebuild only to the FY2024 level, and a 10-year horizon lets the owner-FCF margin mature (~4.0%) before a Gordon terminal at 2.5% on a 9% USD WACC. Leases are in the flows under ASC 842; only finance obligations are debt.
+key_risks_to_valuation: Comps and traffic: every 1pp of sustained comp is roughly 1pp of revenue growth AND ~30-40bp of EBITDA margin through fixed-cost leverage; the bear path (comps -2%/-1% through FY2028, floor-level margin) is what takes the value to the high $40s -- roughly today's price.; The price reset is a one-way bet on margin: ~90bp of Q4 gross-margin deleverage is committed before any traffic response is visible; if traffic does not respond the base case's recovery from 7.9% to 8.5% pre-SBC EBITDA does not happen (each 50bp of mature margin is ~$5/share).; Unit growth: no FY2027 opening target; the base assumes ~32-35 stores/yr (~7% unit growth) fading, the bull ~40, the bear ~25. The ~10% aspiration is not in any scenario.; New-store productivity and cannibalisation as openings move into the Northeast; the base assumes new stores keep earning near-chain-average returns (ROIC incl. leases 16.1%, down from 18.3%).; Capex: FY2026 gross capex ~$340m is 3.6% of sales vs 2.8% in FY2025; the base assumes it eases to 2.8% -- if openings and the tech/supply-chain programme keep capex at 3.5% the owner-FCF margin matures ~0.7pp lower (~$9/share).; Cash tax: the model ramps to 24%; the 10-Q already notes shrinking stock-comp and transferable-credit benefits, so a return of those benefits is upside, not risk.; Leadership: CEO handover (Nick Konat, 2027-01-04) coincides with the price reset, the CTO left 2026-10-12 with no successor, and the executive chairman has a 10b5-1 selling plan; the securities class action (amended complaint due 2026-11-10) is an unmodelled tail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price: Yahoo Finance chart API at inputs.price_as_of (Friday 2026-10-30 regular close); 52-week range 47.35-94.89, so the price sits within 5% of the two-year low set on the guidance cut.
+financials: SFM_Metrics.csv (includes Q1-Q3 FY2026; Q3 is the 13 weeks ended 2026-09-27); FY2025 10-K (SFM_Annual_FY2025.txt) for FY0 flows; Q3-2026 10-Q (SFM_Quarterly_Q3-2026.txt) for the 2026-09-27 balance sheet (cash line 829, finance obligations lines 846/849/1081-1083), diluted shares (line 1315), 39-week SBC (946), buybacks (966), capex (962), cash taxes (976), the 53-week statement (999) and the ~$310m net capex guide (1893).
+qualitative: SFM_Analysis.json refreshed 2026-10-31 (Q3-2026 results, 2026-10-28 guidance cut and strategy reset, CEO succession, CTO departure, Harvest Sherwood settlement, downgrades). The 8-K earnings release is not in Extracted; the 53rd-week basis of the EPS and EBIT guide was resolved arithmetically from the 10-Q's YTD figures plus the Q4 guide quoted in the Analysis JSON.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario narrative: bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The affordability gap to Walmart, Costco and Aldi is structural for a secondary-destination grocer, and management has admitted its pricing strategy 'has not delivered'; the reset buys margin away without buying traffic back. Comps stay negative through FY2028, the new CEO (January 2027, with the CTO seat vacant) slows openings to ~25/yr, the FY2027 'above 5%' EBIT floor becomes the permanent level (~4.8-5.0%), revenue growth is 2-3%, the owner-FCF margin settles near 3.4%, and the business is a slow-growth grocer capped at 14x owner FCF. The securities class action (amended complaint due 2026-11-10) is a tail risk on top of this path, not inside it; Harvest Sherwood is settled and no longer a risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario narrative: base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprouts is a unit-growth story whose comp engine has stalled and whose margin is now being spent to restart it: after +7.3% comps in FY2025 the company has printed -1.7%, -1.0% and -0.9%, guides Q4 at -2% to -4% on traffic down 3.3%, and on 2026-10-28 cut FY2026 EPS to ~$4.80 (incl. the 53rd week) while announcing a broader price reset for January 2027 with only an 'above 5%' FY2027 EBIT-margin floor (vs ~6.4% FY2026, 7.8% FY2025). The base case takes management at its word: FY2027 EBIT 5.5% on revenue that is flat-ish after lapping the 53rd week, then a partial recovery -- comps back to +1-1.5%, unit growth ~7% fading, EBIT rebuilding to ~6.1% (the FY2024 level) by FY2030 and no further. Capex stays above D&amp;A for a growing store base, cash taxes normalise to 24%, and the owner-FCF margin matures at ~4.0% (vs ~4.9% in the prior build). The axes that matter are (1) whether the price reset restores traffic or only resets margin, (2) whether the new CEO keeps opening 35-40 stores a year or slows to protect cash, and (3) how much of the FY2024-25 margin was the +7-11% comp cycle rather than the format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario narrative: bull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The January 2027 affordability reset works the way key-value-item investment has for other grocers: transactions turn positive within two to three quarters, comps run +3% in FY2028-29 on a smaller-store format whose unit economics are intact (ROIC 16% even in a down year), openings hold at ~40/yr with the Northeast proving out, and revenue compounds at 7-8% mid-decade. The margin dips in FY2027 and then rebuilds to a 9.6% pre-SBC EBITDA margin (EBIT ~7.2%) on fixed-cost leverage, private label past 30% of sales and the completed self-distribution network -- below the FY2025 peak. With the stock at ~10x the reset EPS, net cash and $537m of buyback authorization, both earnings and the multiple recover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior valuation_date</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-09-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Current price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price as of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25T20:00:00Z regular close (Yahoo Finance chart API); Friday close, not after-hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance sheet date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owner_fcf_dcf_component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency (model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency (quote)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">millions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcf_engine v1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built at</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28T07:48:46Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drivers file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFM_Drivers.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percents stored as percents; formulas divide by 100. Blue = input, green = link, black = formula.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methodology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">summary: Value Sprouts as a self-funded store-growth compounder whose comps have gone to zero, not as the +7% comp business of FY2025 and not as a broken retailer. The owner-FCF build charges SBC ($31m, 0.35% of sales) in the flows and holds the share count flat; buybacks ($472m in FY2025, $210m in H1-2026) are how the count stays flat, not a source of value. FY2026 is the guided year (53 weeks, flat comps, EPS ~$5.36, capex up on a completed distribution centre); after that growth is new-store arithmetic on a 500-store base fading from 6% to 3%, margins hold below the FY2025 peak, and a 10-year horizon lets the owner-FCF margin mature (~4.9%) before a Gordon terminal at 2.5% on a 9% USD WACC. Leases are in the flows under ASC 842; only finance obligations are debt.
-key_risks_to_valuation: Comps: every 1pp of sustained comp is roughly 1pp of revenue growth AND ~30-40bp of EBITDA margin through fixed-cost leverage; the bear path (comps -1 to -2% through FY2027) is what takes the value to the low $50s.; Harvest Sherwood adversary proceeding ($1bn+ claimed, ~$42m withheld payments; trial 2026-09-21): not modelled. A judgment of even $200-300m would be ~$2-3/share of cash and is not in any scenario.; New-store productivity and cannibalisation as 40+/yr openings move into the Northeast; the base assumes new stores keep earning near-chain-average returns.; Capex: FY2026 gross capex ~$330m is 3.5% of sales vs 2.8% in FY2025; the base assumes it eases to 2.8% -- if openings and remodels keep capex at 3.5% the owner-FCF margin matures ~0.7pp lower (~$10/share).; Cash tax: FY2025's 17.5% cash rate on EBIT depended on stock-comp deductions at ~$150 share prices; the model ramps to 24%, so a return of that benefit is upside, not risk.; CEO succession (Nick Konat, January 2027) during the slowdown; an internal, planned handover but the strategic response to affordability is his to set.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price: Yahoo Finance chart API at inputs.price_as_of (Friday 2026-09-25 regular close); 52-week range 62.485-114.34, so the price sits at the bottom of the range.
-financials: SFM_Metrics.csv re-exported 2026-09-28 from corrected core_metrics (52/53-week labelling fix); FY2025 10-K (SFM_10K_FY2025.txt: cash flow statement lines ~3120-3420, interest income ~2136-2148, diluted shares ~1918-1928, finance obligations ~4455-4470); Q1-2026 10-Q (SFM_10Q_Q1-2026.txt) for Q1 diluted shares and finance obligations; Q2-2026 balance sheet cash $223.9m and diluted 94.41m shares from the CSV/DB; Q2-2026 total finance obligations $113.8m carried from the 2026-08-28 build's Q2 10-Q read (not re-extracted; Q1-2026 verified $97.0m; the difference is ~$0.18/share).
-qualitative: SFM_Analysis.json refreshed 2026-09-28 (Q2-2026 results and guidance, CEO succession, 500th store, Harvest Sherwood trial, Burry position, Deutsche Bank target cut).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario narrative: bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The affordability gap to Walmart, Aldi and Costco is structural for a secondary-destination grocer; comps stay negative through FY2027, the new CEO slows openings, and the margin gives back most of the 2023-25 expansion (pre-SBC EBITDA 8.3%). Revenue growth is 2-3%, the owner-FCF margin settles near 3.5%, and the business is a slow-growth grocer valued at a mid-teens FCF multiple. The Harvest Sherwood $1bn+ claim (trial 2026-09-21, outcome unconfirmed) and the securities class action are tail risks on top of this path, not inside it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario narrative: base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprouts is a unit-growth story whose comp engine has stalled: after +7.3% comps in FY2025 the company has printed -1.7% and -1.0% and guides flat for the year, so FY2026 revenue growth (~6.7% including a 53rd week) is all new stores. The base case assumes the 2024-25 customer surge finishes unwinding in FY2026, comps settle at +1-2% from FY2027, and 40 stores a year on a 500-store base carries revenue growth of 5-6% through the decade, fading to 3%. Margins do not recover to the FY2025 peak: the pre-SBC EBITDA margin dips to ~9.45% on deleverage and rebuilds to 9.8% as private label and self-distribution offset the price investment management has admitted it needs. Capex stays above D&amp;A for a growing store base, cash taxes normalise to 24% as the 2025 stock-comp deductions fade, and the owner-FCF margin matures at ~4.9%. The axes that matter are (1) whether comps are cyclical or structural, (2) new-store productivity as the format goes east, and (3) how much price Sprouts must give back to keep the less-loyal shopper.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario narrative: bull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comps re-accelerate to +3-4% once the FY2025 comparison is lapped: Sprouts Rewards (chainwide since Q4-2025) turns customer data into personalised offers that recover basket size, private label climbs past 30% of sales, and completed meat/seafood self-distribution adds gross margin. Unit growth steps up to 45/yr with the Northeast proving out, revenue compounds at 7-8% mid-decade and the EBITDA margin reaches 10.8%, above the FY2025 peak. The stock's 60% fall from the January 2026 high then reverses on both earnings and multiple.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prior valuation_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prior price_then</t>
   </si>
   <si>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">Prior note</t>
   </si>
   <si>
-    <t xml:space="preserve">Prior was a hand-written 4-year model on reported FCF (SBC not deducted) at a flat 5.3% FCF margin, WACC 8.5% base/bull and 9.5% bear, no terminal cap, built on the pre-fix CSV (FY2020-22 mislabeled/missing). Its JSON also carried a 'weighted_iv_as_published' of 102.64 from an earlier draft; 78.50 is the value the file reported.</t>
+    <t xml:space="preserve">Prior Drivers build of 2026-09-28 (10-year component owner-FCF model, 9% WACC, 25/50/25). Its DCF JSON last carried a refreshed price of 65.20 (2026-10-18) with the same values.</t>
   </si>
   <si>
     <t xml:space="preserve">New valuation_date</t>
@@ -200,16 +200,25 @@
     <t xml:space="preserve">Prior weighted IV</t>
   </si>
   <si>
-    <t xml:space="preserve">Anchor refresh: diluted shares 93.25m -&gt; 94.41m (Q2-2026 diluted weighted average); net debt unchanged at -$110.1m, same 2026-06-28 balance sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount rate: uniform 9.0% USD WACC in all scenarios replaces 8.5% base/bull and 9.5% bear (risk charged once, via weights)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methodology + driver re-judgment on the corrected series: 10-year component owner-FCF build (SBC $31m expensed, flat count, cash tax ramp 21-&gt;24%, capex 3.5%-&gt;2.8% gross, EBITDA 9.45%-&gt;9.8% pre-SBC) with Gordon/16x-cap terminal replaces a 4-year flat 5.3% reported-FCF margin with no cap; the longer horizon and mature ~4.9% owner-FCF margin (vs the prior's FY2026-trough 5.3% reported margin, which was 4.6% after SBC) is most of this</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price move 81.85 -&gt; 62.49 (upside changes from -4% to +35%; no effect on IV)</t>
+    <t xml:space="preserve">Anchor refresh: diluted shares 94.41m -&gt; 93.666m (Q3-2026 diluted weighted average), net cash $110.1m -&gt; $95.6m (2026-09-27 balance sheet: cash $228.7m less $133.1m finance obligations incl. the completed DC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2026 rebuilt to the 2026-10-28 guide (all scenarios): growth 6.7% -&gt; 6.4% (net sales +4.3% on 52 weeks + 53rd week), pre-SBC EBITDA 9.45% -&gt; 8.7% (EBIT ~$605m), capex 3.5% -&gt; 3.6% gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2027+ margin and capex re-judgment (all scenarios): base pre-SBC EBITDA 7.9% in FY2027 (management's &gt;5% EBIT floor) rebuilding only to 8.5% vs the prior 9.55% -&gt; 9.8%; bull matures at 9.6% not 10.8%; bear at 7.3% not 8.3%; capex 3.4% -&gt; 2.8% path slightly higher in years 2-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2027+ growth re-judgment (all scenarios): base 3.0/5.5/5.0/4.5/4.0/3.5 for FY2027-32 vs prior 4.5/6.0/5.5/5.0/4.5/4.0 (53rd-week lap, comps -0.5% in FY2027, unit growth ~7% not ~9%); bull and bear shaded likewise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBC % of revenue 0.35% -&gt; 0.30% on the 39-week FY2026 actual ($19.5m, 0.28%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability weights 25/50/25 -&gt; 30/50/20 (bear: management has delivered the prior bear; bull: price reset unproven)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price move 62.49 -&gt; 49.70 (upside changes from +35% to the new figure; no effect on IV)</t>
   </si>
   <si>
     <t xml:space="preserve">New weighted IV</t>
@@ -297,6 +306,18 @@
   </si>
   <si>
     <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BookValuePerShare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPSBasic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SameStoreSalesGrowth</t>
   </si>
   <si>
     <t xml:space="preserve">FY2011</t>
@@ -957,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>62.49</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1096,7 +1117,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -1126,7 +1147,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.85</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1134,7 +1155,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>54.03</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1142,7 +1163,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>79.95</v>
+        <v>85.24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1150,7 +1171,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>100.08</v>
+        <v>107.72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1158,7 +1179,7 @@
         <v>45</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>78.5</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1182,7 +1203,7 @@
         <v>49</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>62.49</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1190,7 +1211,7 @@
         <v>50</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>59.52</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1198,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>85.24</v>
+        <v>66.05</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1206,7 +1227,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>107.72</v>
+        <v>86.74</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,7 +1235,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>84.43</v>
+        <v>64.96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1227,7 +1248,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>78.5</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1235,7 +1256,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>-1.05</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1243,7 +1264,7 @@
         <v>57</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>-2.27</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1251,7 +1272,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>9.25</v>
+        <v>-15.64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1259,7 +1280,7 @@
         <v>59</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1267,10 +1288,34 @@
         <v>60</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>84.43</v>
-      </c>
-      <c r="C22" s="0" t="s">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>61</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>64.96</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1289,98 +1334,110 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AF16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>310.974</v>
@@ -1427,7 +1484,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>530.309</v>
@@ -1463,7 +1520,7 @@
         <v>716.481</v>
       </c>
       <c r="R3" s="0" t="n">
-        <v>428.332</v>
+        <v>426.544</v>
       </c>
       <c r="S3" s="0" t="n">
         <v>67.211</v>
@@ -1483,20 +1540,32 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>2437.911</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>725.267</v>
       </c>
+      <c r="E4" s="0" t="n">
+        <v>29.7495273617454</v>
+      </c>
       <c r="F4" s="0" t="n">
         <v>139.504</v>
       </c>
+      <c r="G4" s="0" t="n">
+        <v>5.72227616184512</v>
+      </c>
       <c r="H4" s="0" t="n">
         <v>186.721</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>51.326</v>
       </c>
+      <c r="J4" s="0" t="n">
+        <v>2.10532706074996</v>
+      </c>
       <c r="K4" s="0" t="n">
         <v>0.38</v>
       </c>
@@ -1519,7 +1588,7 @@
         <v>658.633</v>
       </c>
       <c r="R4" s="0" t="n">
-        <v>317.062</v>
+        <v>311.24</v>
       </c>
       <c r="S4" s="0" t="n">
         <v>77.652</v>
@@ -1536,29 +1605,53 @@
       <c r="AB4" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD4" s="0" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AE4" s="0" t="n">
+        <v>178</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>92</v>
+        <v>99</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>2967.424</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>885.203</v>
       </c>
+      <c r="E5" s="0" t="n">
+        <v>29.8306881658974</v>
+      </c>
       <c r="F5" s="0" t="n">
         <v>199.711</v>
       </c>
+      <c r="G5" s="0" t="n">
+        <v>6.73011339127809</v>
+      </c>
       <c r="H5" s="0" t="n">
         <v>260.073</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>107.692</v>
       </c>
+      <c r="J5" s="0" t="n">
+        <v>3.62914096536255</v>
+      </c>
       <c r="K5" s="0" t="n">
         <v>0.72</v>
       </c>
+      <c r="L5" s="0" t="n">
+        <v>181.218</v>
+      </c>
       <c r="M5" s="0" t="n">
         <v>127.065</v>
       </c>
+      <c r="N5" s="0" t="n">
+        <v>54.153</v>
+      </c>
       <c r="O5" s="0" t="n">
         <v>685.389</v>
       </c>
@@ -1569,7 +1662,7 @@
         <v>683.684</v>
       </c>
       <c r="R5" s="0" t="n">
-        <v>264.103</v>
+        <v>256.357</v>
       </c>
       <c r="S5" s="0" t="n">
         <v>130.513</v>
@@ -1586,29 +1679,56 @@
       <c r="AB5" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC5" s="0" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AD5" s="0" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>3593.031</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>1051.628</v>
       </c>
+      <c r="E6" s="0" t="n">
+        <v>29.2685479195699</v>
+      </c>
       <c r="F6" s="0" t="n">
         <v>228.754</v>
       </c>
+      <c r="G6" s="0" t="n">
+        <v>6.36660245903807</v>
+      </c>
       <c r="H6" s="0" t="n">
         <v>297.923</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>128.991</v>
       </c>
+      <c r="J6" s="0" t="n">
+        <v>3.59003303895792</v>
+      </c>
       <c r="K6" s="0" t="n">
         <v>0.84</v>
       </c>
+      <c r="L6" s="0" t="n">
+        <v>239.898</v>
+      </c>
       <c r="M6" s="0" t="n">
         <v>125.313</v>
       </c>
+      <c r="N6" s="0" t="n">
+        <v>114.585</v>
+      </c>
       <c r="O6" s="0" t="n">
         <v>822.992</v>
       </c>
@@ -1636,10 +1756,19 @@
       <c r="AB6" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC6" s="0" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="AD6" s="0" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE6" s="0" t="n">
+        <v>217</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>4046.385</v>
@@ -1707,10 +1836,19 @@
       <c r="AB7" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC7" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD7" s="0" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE7" s="0" t="n">
+        <v>253</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>4664.612</v>
@@ -1778,10 +1916,13 @@
       <c r="AB8" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AE8" s="0" t="n">
+        <v>285</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>5207.336</v>
@@ -1849,10 +1990,16 @@
       <c r="AB9" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AE9" s="0" t="n">
+        <v>313</v>
+      </c>
+      <c r="AF9" s="0" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>5634.835</v>
@@ -1917,10 +2064,19 @@
       <c r="AB10" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AD10" s="0" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" s="0" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF10" s="0" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>6468.759</v>
@@ -1970,6 +2126,9 @@
       <c r="Q11" s="0" t="n">
         <v>1925.111</v>
       </c>
+      <c r="R11" s="0" t="n">
+        <v>250</v>
+      </c>
       <c r="S11" s="0" t="n">
         <v>169.697</v>
       </c>
@@ -1985,10 +2144,22 @@
       <c r="AB11" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC11" s="0" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AD11" s="0" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE11" s="0" t="n">
+        <v>362</v>
+      </c>
+      <c r="AF11" s="0" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>6099.869</v>
@@ -2056,10 +2227,22 @@
       <c r="AB12" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC12" s="0" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="AD12" s="0" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE12" s="0" t="n">
+        <v>374</v>
+      </c>
+      <c r="AF12" s="0" t="n">
+        <v>-6.7</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>6404.223</v>
@@ -2127,10 +2310,22 @@
       <c r="AB13" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC13" s="0" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="AD13" s="0" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE13" s="0" t="n">
+        <v>386</v>
+      </c>
+      <c r="AF13" s="0" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>6837.384</v>
@@ -2198,10 +2393,22 @@
       <c r="AB14" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC14" s="0" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AD14" s="0" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE14" s="0" t="n">
+        <v>407</v>
+      </c>
+      <c r="AF14" s="0" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>7719.29</v>
@@ -2251,6 +2458,9 @@
       <c r="Q15" s="0" t="n">
         <v>2318.806</v>
       </c>
+      <c r="R15" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" s="0" t="n">
         <v>265.159</v>
       </c>
@@ -2266,10 +2476,22 @@
       <c r="AB15" s="0" t="s">
         <v>14</v>
       </c>
+      <c r="AC15" s="0" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="AD15" s="0" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AE15" s="0" t="n">
+        <v>440</v>
+      </c>
+      <c r="AF15" s="0" t="n">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>8806.159</v>
@@ -2319,6 +2541,9 @@
       <c r="Q16" s="0" t="n">
         <v>2755.575</v>
       </c>
+      <c r="R16" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="S16" s="0" t="n">
         <v>257.282</v>
       </c>
@@ -2333,6 +2558,18 @@
       </c>
       <c r="AB16" s="0" t="s">
         <v>14</v>
+      </c>
+      <c r="AC16" s="0" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AD16" s="0" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AE16" s="0" t="n">
+        <v>477</v>
+      </c>
+      <c r="AF16" s="0" t="n">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2596,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>37</v>
@@ -2367,31 +2604,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>62.49</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>94.41</v>
+        <v>93.666</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-110.104</v>
+        <v>-95.578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
@@ -2399,7 +2636,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>15</v>
@@ -2407,7 +2644,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>8806.159</v>
@@ -2415,23 +2652,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -2439,51 +2676,51 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>3</v>
@@ -2492,13 +2729,13 @@
         <v>3</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>2</v>
@@ -2509,77 +2746,77 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9.2</v>
+        <v>8.6</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>8.7</v>
+        <v>7.4</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -2614,7 +2851,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>2</v>
@@ -2649,16 +2886,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>2.6</v>
@@ -2684,7 +2921,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>21</v>
@@ -2719,7 +2956,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>9</v>
@@ -2727,7 +2964,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>2</v>
@@ -2735,7 +2972,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>14</v>
@@ -2743,7 +2980,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>2</v>
@@ -2751,74 +2988,74 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="H27" s="3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>3</v>
@@ -2829,77 +3066,77 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9.45</v>
+        <v>8.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>9.55</v>
+        <v>7.9</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>9.65</v>
+        <v>8.1</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>9.75</v>
+        <v>8.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>0</v>
@@ -2934,7 +3171,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>2</v>
@@ -2969,13 +3206,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>3.2</v>
@@ -3004,7 +3241,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>21</v>
@@ -3039,7 +3276,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>9</v>
@@ -3047,7 +3284,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>2.5</v>
@@ -3055,7 +3292,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>16</v>
@@ -3063,7 +3300,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>2</v>
@@ -3071,7 +3308,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0.5</v>
@@ -3079,66 +3316,66 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>4</v>
@@ -3149,77 +3386,77 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C42" s="3" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>10.6</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -3254,7 +3491,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>2</v>
@@ -3289,31 +3526,31 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C46" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D46" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="G46" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="H46" s="3" t="n">
         <v>3.1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>3</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>2.9</v>
@@ -3324,7 +3561,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>21</v>
@@ -3359,7 +3596,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B48" s="3" t="n">
         <v>9</v>
@@ -3367,7 +3604,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>3</v>
@@ -3375,7 +3612,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>16</v>
@@ -3383,7 +3620,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B51" s="3" t="n">
         <v>2</v>
@@ -3391,10 +3628,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3421,50 +3658,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -3512,19 +3749,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C13</f>
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">Assumptions!D13</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">Assumptions!E13</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">Assumptions!F13</f>
@@ -3536,7 +3773,7 @@
       </c>
       <c r="H5" s="4" t="n">
         <f aca="false">Assumptions!H13</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="4" t="n">
         <f aca="false">Assumptions!I13</f>
@@ -3544,7 +3781,7 @@
       </c>
       <c r="J5" s="4" t="n">
         <f aca="false">Assumptions!J13</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4" t="n">
         <f aca="false">Assumptions!K13</f>
@@ -3557,370 +3794,370 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>8806.159</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">B6*(1+C5/100)</f>
-        <v>9334.52854</v>
+        <v>9352.140858</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">C6*(1+D5/100)</f>
-        <v>9474.5464681</v>
+        <v>9398.90156229</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">D6*(1+E5/100)</f>
-        <v>9711.4101298025</v>
+        <v>9680.8686091587</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">E6*(1+F5/100)</f>
-        <v>10002.7524336966</v>
+        <v>9971.29466743346</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">F6*(1+G5/100)</f>
-        <v>10302.8350067075</v>
+        <v>10270.4335074565</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">G6*(1+H5/100)</f>
-        <v>10611.9200569087</v>
+        <v>10527.1943451429</v>
       </c>
       <c r="I6" s="0" t="n">
         <f aca="false">H6*(1+I5/100)</f>
-        <v>10877.2180583314</v>
+        <v>10790.3742037714</v>
       </c>
       <c r="J6" s="0" t="n">
         <f aca="false">I6*(1+J5/100)</f>
-        <v>11149.1485097897</v>
+        <v>11006.1816878469</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">J6*(1+K5/100)</f>
-        <v>11372.1314799855</v>
+        <v>11226.3053216038</v>
       </c>
       <c r="L6" s="0" t="n">
         <f aca="false">K6*(1+L5/100)</f>
-        <v>11599.5741095852</v>
+        <v>11450.8314280359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C14</f>
-        <v>9.2</v>
+        <v>8.6</v>
       </c>
       <c r="D7" s="4" t="n">
         <f aca="false">Assumptions!D14</f>
-        <v>8.7</v>
+        <v>7.4</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">Assumptions!E14</f>
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">Assumptions!F14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="G7" s="4" t="n">
         <f aca="false">Assumptions!G14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="H7" s="4" t="n">
         <f aca="false">Assumptions!H14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="I7" s="4" t="n">
         <f aca="false">Assumptions!I14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="J7" s="4" t="n">
         <f aca="false">Assumptions!J14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="K7" s="4" t="n">
         <f aca="false">Assumptions!K14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
       <c r="L7" s="4" t="n">
         <f aca="false">Assumptions!L14</f>
-        <v>8.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">C6*C7/100</f>
-        <v>858.77662568</v>
+        <v>804.284113788</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">D6*D7/100</f>
-        <v>824.2855427247</v>
+        <v>695.51871560946</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">E6*E7/100</f>
-        <v>815.75845090341</v>
+        <v>706.703408468585</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">F6*F7/100</f>
-        <v>830.228451996816</v>
+        <v>727.904510722643</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">G6*G7/100</f>
-        <v>855.13530555672</v>
+        <v>749.741646044322</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">H6*H7/100</f>
-        <v>880.789364723422</v>
+        <v>768.48518719543</v>
       </c>
       <c r="I8" s="0" t="n">
         <f aca="false">I6*I7/100</f>
-        <v>902.809098841507</v>
+        <v>787.697316875315</v>
       </c>
       <c r="J8" s="0" t="n">
         <f aca="false">J6*J7/100</f>
-        <v>925.379326312544</v>
+        <v>803.451263212822</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">K6*K7/100</f>
-        <v>943.886912838795</v>
+        <v>819.520288477078</v>
       </c>
       <c r="L8" s="0" t="n">
         <f aca="false">L6*L7/100</f>
-        <v>962.764651095571</v>
+        <v>835.91069424662</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="4" t="n">
         <f aca="false">Assumptions!D15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">Assumptions!E15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">Assumptions!F15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="4" t="n">
         <f aca="false">Assumptions!G15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="4" t="n">
         <f aca="false">Assumptions!H15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="4" t="n">
         <f aca="false">Assumptions!I15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="4" t="n">
         <f aca="false">Assumptions!J15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="4" t="n">
         <f aca="false">Assumptions!K15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L9" s="4" t="n">
         <f aca="false">Assumptions!L15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
-        <v>-32.67084989</v>
+        <v>-28.056422574</v>
       </c>
       <c r="D10" s="0" t="n">
         <f aca="false">-D6*D9/100</f>
-        <v>-33.16091263835</v>
+        <v>-28.19670468687</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">-E6*E9/100</f>
-        <v>-33.9899354543087</v>
+        <v>-29.0426058274761</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">-F6*F9/100</f>
-        <v>-35.009633517938</v>
+        <v>-29.9138840023004</v>
       </c>
       <c r="G10" s="0" t="n">
         <f aca="false">-G6*G9/100</f>
-        <v>-36.0599225234761</v>
+        <v>-30.8113005223694</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">-H6*H9/100</f>
-        <v>-37.1417201991804</v>
+        <v>-31.5815830354286</v>
       </c>
       <c r="I10" s="0" t="n">
         <f aca="false">-I6*I9/100</f>
-        <v>-38.0702632041599</v>
+        <v>-32.3711226113143</v>
       </c>
       <c r="J10" s="0" t="n">
         <f aca="false">-J6*J9/100</f>
-        <v>-39.0220197842639</v>
+        <v>-33.0185450635406</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">-K6*K9/100</f>
-        <v>-39.8024601799492</v>
+        <v>-33.6789159648114</v>
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">-L6*L9/100</f>
-        <v>-40.5985093835482</v>
+        <v>-34.3524942841077</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
-        <v>826.10577579</v>
+        <v>776.227691214</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">D8+D10+D24</f>
-        <v>791.12463008635</v>
+        <v>667.32201092259</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">E8+E10+E24</f>
-        <v>781.768515449101</v>
+        <v>677.660802641109</v>
       </c>
       <c r="F11" s="0" t="n">
         <f aca="false">F8+F10+F24</f>
-        <v>795.218818478877</v>
+        <v>697.990626720342</v>
       </c>
       <c r="G11" s="0" t="n">
         <f aca="false">G8+G10+G24</f>
-        <v>819.075383033244</v>
+        <v>718.930345521952</v>
       </c>
       <c r="H11" s="0" t="n">
         <f aca="false">H8+H10+H24</f>
-        <v>843.647644524241</v>
+        <v>736.903604160001</v>
       </c>
       <c r="I11" s="0" t="n">
         <f aca="false">I8+I10+I24</f>
-        <v>864.738835637347</v>
+        <v>755.326194264001</v>
       </c>
       <c r="J11" s="0" t="n">
         <f aca="false">J8+J10+J24</f>
-        <v>886.357306528281</v>
+        <v>770.432718149281</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">K8+K10+K24</f>
-        <v>904.084452658846</v>
+        <v>785.841372512267</v>
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">L8+L10+L24</f>
-        <v>922.166141712023</v>
+        <v>801.558199962512</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C17/100</f>
-        <v>-186.6905708</v>
+        <v>-187.04281716</v>
       </c>
       <c r="D12" s="4" t="n">
         <f aca="false">-D6*Assumptions!D17/100</f>
-        <v>-198.9654758301</v>
+        <v>-197.37693280809</v>
       </c>
       <c r="E12" s="4" t="n">
         <f aca="false">-E6*Assumptions!E17/100</f>
-        <v>-208.795317790754</v>
+        <v>-208.138675096912</v>
       </c>
       <c r="F12" s="4" t="n">
         <f aca="false">-F6*Assumptions!F17/100</f>
-        <v>-220.060553541325</v>
+        <v>-219.368482683536</v>
       </c>
       <c r="G12" s="4" t="n">
         <f aca="false">-G6*Assumptions!G17/100</f>
-        <v>-226.662370147564</v>
+        <v>-225.949537164042</v>
       </c>
       <c r="H12" s="4" t="n">
         <f aca="false">-H6*Assumptions!H17/100</f>
-        <v>-233.462241251991</v>
+        <v>-231.598275593143</v>
       </c>
       <c r="I12" s="4" t="n">
         <f aca="false">-I6*Assumptions!I17/100</f>
-        <v>-239.298797283291</v>
+        <v>-237.388232482972</v>
       </c>
       <c r="J12" s="4" t="n">
         <f aca="false">-J6*Assumptions!J17/100</f>
-        <v>-245.281267215373</v>
+        <v>-242.135997132631</v>
       </c>
       <c r="K12" s="4" t="n">
         <f aca="false">-K6*Assumptions!K17/100</f>
-        <v>-250.186892559681</v>
+        <v>-246.978717075284</v>
       </c>
       <c r="L12" s="4" t="n">
         <f aca="false">-L6*Assumptions!L17/100</f>
-        <v>-255.190630410874</v>
+        <v>-251.91829141679</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
-        <v>639.41520499</v>
+        <v>589.184874054</v>
       </c>
       <c r="D13" s="0" t="n">
         <f aca="false">D11+D12</f>
-        <v>592.15915425625</v>
+        <v>469.9450781145</v>
       </c>
       <c r="E13" s="0" t="n">
         <f aca="false">E11+E12</f>
-        <v>572.973197658347</v>
+        <v>469.522127544197</v>
       </c>
       <c r="F13" s="0" t="n">
         <f aca="false">F11+F12</f>
-        <v>575.158264937553</v>
+        <v>478.622144036806</v>
       </c>
       <c r="G13" s="0" t="n">
         <f aca="false">G11+G12</f>
-        <v>592.41301288568</v>
+        <v>492.98080835791</v>
       </c>
       <c r="H13" s="0" t="n">
         <f aca="false">H11+H12</f>
-        <v>610.18540327225</v>
+        <v>505.305328566858</v>
       </c>
       <c r="I13" s="0" t="n">
         <f aca="false">I11+I12</f>
-        <v>625.440038354056</v>
+        <v>517.937961781029</v>
       </c>
       <c r="J13" s="0" t="n">
         <f aca="false">J11+J12</f>
-        <v>641.076039312907</v>
+        <v>528.29672101665</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">K11+K12</f>
-        <v>653.897560099165</v>
+        <v>538.862655436983</v>
       </c>
       <c r="L13" s="0" t="n">
         <f aca="false">L11+L12</f>
-        <v>666.975511301149</v>
+        <v>549.639908545723</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C19</f>
@@ -3965,232 +4202,232 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
-        <v>505.1380119421</v>
+        <v>465.45605050266</v>
       </c>
       <c r="D15" s="0" t="n">
         <f aca="false">D13-MAX(0,D13)*D14/100</f>
-        <v>461.884140319875</v>
+        <v>366.55716092931</v>
       </c>
       <c r="E15" s="0" t="n">
         <f aca="false">E13-MAX(0,E13)*E14/100</f>
-        <v>441.189362196927</v>
+        <v>361.532038209032</v>
       </c>
       <c r="F15" s="0" t="n">
         <f aca="false">F13-MAX(0,F13)*F14/100</f>
-        <v>437.12028135254</v>
+        <v>363.752829467973</v>
       </c>
       <c r="G15" s="0" t="n">
         <f aca="false">G13-MAX(0,G13)*G14/100</f>
-        <v>450.233889793117</v>
+        <v>374.665414352012</v>
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">H13-MAX(0,H13)*H14/100</f>
-        <v>463.74090648691</v>
+        <v>384.032049710812</v>
       </c>
       <c r="I15" s="0" t="n">
         <f aca="false">I13-MAX(0,I13)*I14/100</f>
-        <v>475.334429149083</v>
+        <v>393.632850953582</v>
       </c>
       <c r="J15" s="0" t="n">
         <f aca="false">J13-MAX(0,J13)*J14/100</f>
-        <v>487.21778987781</v>
+        <v>401.505507972654</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">K13-MAX(0,K13)*K14/100</f>
-        <v>496.962145675366</v>
+        <v>409.535618132107</v>
       </c>
       <c r="L15" s="0" t="n">
         <f aca="false">L13-MAX(0,L13)*L14/100</f>
-        <v>506.901388588873</v>
+        <v>417.726330494749</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
-        <v>186.6905708</v>
+        <v>187.04281716</v>
       </c>
       <c r="D16" s="0" t="n">
         <f aca="false">-D12</f>
-        <v>198.9654758301</v>
+        <v>197.37693280809</v>
       </c>
       <c r="E16" s="0" t="n">
         <f aca="false">-E12</f>
-        <v>208.795317790754</v>
+        <v>208.138675096912</v>
       </c>
       <c r="F16" s="0" t="n">
         <f aca="false">-F12</f>
-        <v>220.060553541325</v>
+        <v>219.368482683536</v>
       </c>
       <c r="G16" s="0" t="n">
         <f aca="false">-G12</f>
-        <v>226.662370147564</v>
+        <v>225.949537164042</v>
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">-H12</f>
-        <v>233.462241251991</v>
+        <v>231.598275593143</v>
       </c>
       <c r="I16" s="0" t="n">
         <f aca="false">-I12</f>
-        <v>239.298797283291</v>
+        <v>237.388232482972</v>
       </c>
       <c r="J16" s="0" t="n">
         <f aca="false">-J12</f>
-        <v>245.281267215373</v>
+        <v>242.135997132631</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">-K12</f>
-        <v>250.186892559681</v>
+        <v>246.978717075284</v>
       </c>
       <c r="L16" s="0" t="n">
         <f aca="false">-L12</f>
-        <v>255.190630410874</v>
+        <v>251.91829141679</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C18/100</f>
-        <v>-317.37397036</v>
+        <v>-336.677070888</v>
       </c>
       <c r="D17" s="4" t="n">
         <f aca="false">-D6*Assumptions!D18/100</f>
-        <v>-284.236394043</v>
+        <v>-291.36594843099</v>
       </c>
       <c r="E17" s="4" t="n">
         <f aca="false">-E6*Assumptions!E18/100</f>
-        <v>-262.208073504667</v>
+        <v>-271.064321056444</v>
       </c>
       <c r="F17" s="4" t="n">
         <f aca="false">-F6*Assumptions!F18/100</f>
-        <v>-260.071563276111</v>
+        <v>-259.25366135327</v>
       </c>
       <c r="G17" s="4" t="n">
         <f aca="false">-G6*Assumptions!G18/100</f>
-        <v>-257.570875167687</v>
+        <v>-256.760837686412</v>
       </c>
       <c r="H17" s="4" t="n">
         <f aca="false">-H6*Assumptions!H18/100</f>
-        <v>-265.298001422717</v>
+        <v>-263.179858628572</v>
       </c>
       <c r="I17" s="4" t="n">
         <f aca="false">-I6*Assumptions!I18/100</f>
-        <v>-271.930451458285</v>
+        <v>-269.759355094286</v>
       </c>
       <c r="J17" s="4" t="n">
         <f aca="false">-J6*Assumptions!J18/100</f>
-        <v>-278.728712744742</v>
+        <v>-275.154542196172</v>
       </c>
       <c r="K17" s="4" t="n">
         <f aca="false">-K6*Assumptions!K18/100</f>
-        <v>-284.303286999637</v>
+        <v>-280.657633040095</v>
       </c>
       <c r="L17" s="4" t="n">
         <f aca="false">-L6*Assumptions!L18/100</f>
-        <v>-289.98935273963</v>
+        <v>-286.270785700897</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$23/100</f>
-        <v>10.5673908</v>
+        <v>10.91963716</v>
       </c>
       <c r="D18" s="4" t="n">
         <f aca="false">(D6-C6)*Assumptions!$B$23/100</f>
-        <v>2.80035856199997</v>
+        <v>0.935214085799962</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">(E6-D6)*Assumptions!$B$23/100</f>
-        <v>4.73727323404997</v>
+        <v>5.639340937374</v>
       </c>
       <c r="F18" s="4" t="n">
         <f aca="false">(F6-E6)*Assumptions!$B$23/100</f>
-        <v>5.82684607788149</v>
+        <v>5.80852116549522</v>
       </c>
       <c r="G18" s="4" t="n">
         <f aca="false">(G6-F6)*Assumptions!$B$23/100</f>
-        <v>6.00165146021795</v>
+        <v>5.98277680046009</v>
       </c>
       <c r="H18" s="4" t="n">
         <f aca="false">(H6-G6)*Assumptions!$B$23/100</f>
-        <v>6.18170100402447</v>
+        <v>5.1352167537282</v>
       </c>
       <c r="I18" s="4" t="n">
         <f aca="false">(I6-H6)*Assumptions!$B$23/100</f>
-        <v>5.30596002845432</v>
+        <v>5.26359717257143</v>
       </c>
       <c r="J18" s="4" t="n">
         <f aca="false">(J6-I6)*Assumptions!$B$23/100</f>
-        <v>5.43860902916567</v>
+        <v>4.31614968150858</v>
       </c>
       <c r="K18" s="4" t="n">
         <f aca="false">(K6-J6)*Assumptions!$B$23/100</f>
-        <v>4.45965940391587</v>
+        <v>4.40247267513874</v>
       </c>
       <c r="L18" s="4" t="n">
         <f aca="false">(L6-K6)*Assumptions!$B$23/100</f>
-        <v>4.54885259199418</v>
+        <v>4.49052212864153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
-        <v>385.0220031821</v>
+        <v>326.74143393466</v>
       </c>
       <c r="D19" s="0" t="n">
         <f aca="false">D15+D16+D17+D18</f>
-        <v>379.413580668975</v>
+        <v>273.50335939221</v>
       </c>
       <c r="E19" s="0" t="n">
         <f aca="false">E15+E16+E17+E18</f>
-        <v>392.513879717064</v>
+        <v>304.245733186874</v>
       </c>
       <c r="F19" s="0" t="n">
         <f aca="false">F15+F16+F17+F18</f>
-        <v>402.936117695635</v>
+        <v>329.676171963734</v>
       </c>
       <c r="G19" s="0" t="n">
         <f aca="false">G15+G16+G17+G18</f>
-        <v>425.327036233212</v>
+        <v>349.836890630102</v>
       </c>
       <c r="H19" s="0" t="n">
         <f aca="false">H15+H16+H17+H18</f>
-        <v>438.086847320208</v>
+        <v>357.585683429112</v>
       </c>
       <c r="I19" s="0" t="n">
         <f aca="false">I15+I16+I17+I18</f>
-        <v>448.008735002543</v>
+        <v>366.525325514839</v>
       </c>
       <c r="J19" s="0" t="n">
         <f aca="false">J15+J16+J17+J18</f>
-        <v>459.208953377606</v>
+        <v>372.803112590622</v>
       </c>
       <c r="K19" s="0" t="n">
         <f aca="false">K15+K16+K17+K18</f>
-        <v>467.305410639325</v>
+        <v>380.259174842434</v>
       </c>
       <c r="L19" s="0" t="n">
         <f aca="false">L15+L16+L17+L18</f>
-        <v>476.651518852112</v>
+        <v>387.864358339283</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -4235,52 +4472,52 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
-        <v>353.231195579908</v>
+        <v>299.762783426294</v>
       </c>
       <c r="D21" s="0" t="n">
         <f aca="false">D19*D20</f>
-        <v>319.344820022704</v>
+        <v>230.202305691617</v>
       </c>
       <c r="E21" s="0" t="n">
         <f aca="false">E19*E20</f>
-        <v>303.092733612192</v>
+        <v>234.93352904597</v>
       </c>
       <c r="F21" s="0" t="n">
         <f aca="false">F19*F20</f>
-        <v>285.450104224321</v>
+        <v>233.550911706574</v>
       </c>
       <c r="G21" s="0" t="n">
         <f aca="false">G19*G20</f>
-        <v>276.433390289218</v>
+        <v>227.369975305525</v>
       </c>
       <c r="H21" s="0" t="n">
         <f aca="false">H19*H20</f>
-        <v>261.216873392564</v>
+        <v>213.216659588554</v>
       </c>
       <c r="I21" s="0" t="n">
         <f aca="false">I19*I20</f>
-        <v>245.076120035326</v>
+        <v>200.501904658961</v>
       </c>
       <c r="J21" s="0" t="n">
         <f aca="false">J19*J20</f>
-        <v>230.461489024045</v>
+        <v>187.097311166283</v>
       </c>
       <c r="K21" s="0" t="n">
         <f aca="false">K19*K20</f>
-        <v>215.160392576618</v>
+        <v>175.081887513403</v>
       </c>
       <c r="L21" s="0" t="n">
         <f aca="false">L19*L20</f>
-        <v>201.342752686376</v>
+        <v>163.838096572175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C16</f>
@@ -4325,7 +4562,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -4370,12 +4607,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$20</f>
@@ -4384,7 +4621,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$21</f>
@@ -4393,7 +4630,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$22</f>
@@ -4402,124 +4639,124 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
-        <v>2690.80987144327</v>
+        <v>2165.55536467536</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
-        <v>476.651518852112</v>
+        <v>387.864358339283</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
-        <v>6945.49356041648</v>
+        <v>5651.73779294384</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
-        <v>6673.12126392956</v>
+        <v>5430.10101674996</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
-        <v>6673.12126392956</v>
+        <v>5430.10101674996</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
-        <v>2818.79853760927</v>
+        <v>2293.73335201045</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
-        <v>5509.60840905254</v>
+        <v>4459.28871668581</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
-        <v>5619.71240905254</v>
+        <v>4554.86671668581</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>59.5245462244735</v>
+        <v>48.6288163974741</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
-        <v>-0.0474548531849344</v>
+        <v>-0.0215529899904607</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
-        <v>230.400157865477</v>
+        <v>196.243287125438</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
-        <v>249.889058423087</v>
+        <v>211.444030371686</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>64.611816813273</v>
+        <v>52.981381015341</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -4528,20 +4765,20 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
-        <v>3739.88114791657</v>
+        <v>3043.24342696976</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>32.9918439767351</v>
+        <v>26.898179438958</v>
       </c>
     </row>
   </sheetData>
@@ -4568,50 +4805,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -4659,39 +4896,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C27</f>
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">Assumptions!D27</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">Assumptions!E27</f>
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">Assumptions!F27</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">Assumptions!G27</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H5" s="4" t="n">
         <f aca="false">Assumptions!H27</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4" t="n">
         <f aca="false">Assumptions!I27</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="4" t="n">
         <f aca="false">Assumptions!J27</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4" t="n">
         <f aca="false">Assumptions!K27</f>
@@ -4704,370 +4941,370 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>8806.159</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">B6*(1+C5/100)</f>
-        <v>9396.171653</v>
+        <v>9369.753176</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">C6*(1+D5/100)</f>
-        <v>9818.999377385</v>
+        <v>9650.84577128</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">D6*(1+E5/100)</f>
-        <v>10408.1393400281</v>
+        <v>10181.6422887004</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">E6*(1+F5/100)</f>
-        <v>10980.5870037296</v>
+        <v>10690.7244031354</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">F6*(1+G5/100)</f>
-        <v>11529.6163539161</v>
+        <v>11171.8070012765</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">G6*(1+H5/100)</f>
-        <v>12048.4490898424</v>
+        <v>11618.6792813276</v>
       </c>
       <c r="I6" s="0" t="n">
         <f aca="false">H6*(1+I5/100)</f>
-        <v>12530.387053436</v>
+        <v>12025.333056174</v>
       </c>
       <c r="J6" s="0" t="n">
         <f aca="false">I6*(1+J5/100)</f>
-        <v>12968.9506003063</v>
+        <v>12386.0930478593</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">J6*(1+K5/100)</f>
-        <v>13358.0191183155</v>
+        <v>12757.675839295</v>
       </c>
       <c r="L6" s="0" t="n">
         <f aca="false">K6*(1+L5/100)</f>
-        <v>13758.759691865</v>
+        <v>13140.4061144739</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C28</f>
-        <v>9.45</v>
+        <v>8.7</v>
       </c>
       <c r="D7" s="4" t="n">
         <f aca="false">Assumptions!D28</f>
-        <v>9.55</v>
+        <v>7.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">Assumptions!E28</f>
-        <v>9.65</v>
+        <v>8.1</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">Assumptions!F28</f>
-        <v>9.75</v>
+        <v>8.3</v>
       </c>
       <c r="G7" s="4" t="n">
         <f aca="false">Assumptions!G28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="H7" s="4" t="n">
         <f aca="false">Assumptions!H28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="I7" s="4" t="n">
         <f aca="false">Assumptions!I28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="J7" s="4" t="n">
         <f aca="false">Assumptions!J28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="K7" s="4" t="n">
         <f aca="false">Assumptions!K28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
       <c r="L7" s="4" t="n">
         <f aca="false">Assumptions!L28</f>
-        <v>9.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">C6*C7/100</f>
-        <v>887.9382212085</v>
+        <v>815.168526312</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">D6*D7/100</f>
-        <v>937.714440540267</v>
+        <v>762.41681593112</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">E6*E7/100</f>
-        <v>1004.38544631271</v>
+        <v>824.713025384732</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">F6*F7/100</f>
-        <v>1070.60723286364</v>
+        <v>887.33012546024</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">G6*G7/100</f>
-        <v>1129.90240268378</v>
+        <v>949.603595108504</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">H6*H7/100</f>
-        <v>1180.74801080455</v>
+        <v>987.587738912844</v>
       </c>
       <c r="I8" s="0" t="n">
         <f aca="false">I6*I7/100</f>
-        <v>1227.97793123673</v>
+        <v>1022.15330977479</v>
       </c>
       <c r="J8" s="0" t="n">
         <f aca="false">J6*J7/100</f>
-        <v>1270.95715883002</v>
+        <v>1052.81790906804</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">K6*K7/100</f>
-        <v>1309.08587359492</v>
+        <v>1084.40244634008</v>
       </c>
       <c r="L8" s="0" t="n">
         <f aca="false">L6*L7/100</f>
-        <v>1348.35844980277</v>
+        <v>1116.93451973028</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="4" t="n">
         <f aca="false">Assumptions!D29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">Assumptions!E29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">Assumptions!F29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="4" t="n">
         <f aca="false">Assumptions!G29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="4" t="n">
         <f aca="false">Assumptions!H29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="4" t="n">
         <f aca="false">Assumptions!I29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="4" t="n">
         <f aca="false">Assumptions!J29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="4" t="n">
         <f aca="false">Assumptions!K29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L9" s="4" t="n">
         <f aca="false">Assumptions!L29</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
-        <v>-32.8866007855</v>
+        <v>-28.109259528</v>
       </c>
       <c r="D10" s="0" t="n">
         <f aca="false">-D6*D9/100</f>
-        <v>-34.3664978208475</v>
+        <v>-28.95253731384</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">-E6*E9/100</f>
-        <v>-36.4284876900983</v>
+        <v>-30.5449268661012</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">-F6*F9/100</f>
-        <v>-38.4320545130538</v>
+        <v>-32.0721732094063</v>
       </c>
       <c r="G10" s="0" t="n">
         <f aca="false">-G6*G9/100</f>
-        <v>-40.3536572387065</v>
+        <v>-33.5154210038295</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">-H6*H9/100</f>
-        <v>-42.1695718144482</v>
+        <v>-34.8560378439827</v>
       </c>
       <c r="I10" s="0" t="n">
         <f aca="false">-I6*I9/100</f>
-        <v>-43.8563546870262</v>
+        <v>-36.0759991685221</v>
       </c>
       <c r="J10" s="0" t="n">
         <f aca="false">-J6*J9/100</f>
-        <v>-45.3913271010721</v>
+        <v>-37.1582791435778</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">-K6*K9/100</f>
-        <v>-46.7530669141042</v>
+        <v>-38.2730275178851</v>
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">-L6*L9/100</f>
-        <v>-48.1556589215274</v>
+        <v>-39.4212183434217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
-        <v>855.051620423</v>
+        <v>787.059266784</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">D8+D10+D24</f>
-        <v>903.34794271942</v>
+        <v>733.46427861728</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">E8+E10+E24</f>
-        <v>967.956958622613</v>
+        <v>794.168098518631</v>
       </c>
       <c r="F11" s="0" t="n">
         <f aca="false">F8+F10+F24</f>
-        <v>1032.17517835059</v>
+        <v>855.257952250834</v>
       </c>
       <c r="G11" s="0" t="n">
         <f aca="false">G8+G10+G24</f>
-        <v>1089.54874544507</v>
+        <v>916.088174104674</v>
       </c>
       <c r="H11" s="0" t="n">
         <f aca="false">H8+H10+H24</f>
-        <v>1138.5784389901</v>
+        <v>952.731701068861</v>
       </c>
       <c r="I11" s="0" t="n">
         <f aca="false">I8+I10+I24</f>
-        <v>1184.12157654971</v>
+        <v>986.077310606271</v>
       </c>
       <c r="J11" s="0" t="n">
         <f aca="false">J8+J10+J24</f>
-        <v>1225.56583172895</v>
+        <v>1015.65962992446</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">K8+K10+K24</f>
-        <v>1262.33280668081</v>
+        <v>1046.12941882219</v>
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">L8+L10+L24</f>
-        <v>1300.20279088124</v>
+        <v>1077.51330138686</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C31/100</f>
-        <v>-187.92343306</v>
+        <v>-187.39506352</v>
       </c>
       <c r="D12" s="4" t="n">
         <f aca="false">-D6*Assumptions!D31/100</f>
-        <v>-201.289487236392</v>
+        <v>-197.84233831124</v>
       </c>
       <c r="E12" s="4" t="n">
         <f aca="false">-E6*Assumptions!E31/100</f>
-        <v>-218.57092614059</v>
+        <v>-213.814488062708</v>
       </c>
       <c r="F12" s="4" t="n">
         <f aca="false">-F6*Assumptions!F31/100</f>
-        <v>-230.592327078323</v>
+        <v>-224.505212465844</v>
       </c>
       <c r="G12" s="4" t="n">
         <f aca="false">-G6*Assumptions!G31/100</f>
-        <v>-242.121943432239</v>
+        <v>-234.607947026807</v>
       </c>
       <c r="H12" s="4" t="n">
         <f aca="false">-H6*Assumptions!H31/100</f>
-        <v>-253.017430886689</v>
+        <v>-243.992264907879</v>
       </c>
       <c r="I12" s="4" t="n">
         <f aca="false">-I6*Assumptions!I31/100</f>
-        <v>-263.138128122157</v>
+        <v>-252.531994179655</v>
       </c>
       <c r="J12" s="4" t="n">
         <f aca="false">-J6*Assumptions!J31/100</f>
-        <v>-272.347962606433</v>
+        <v>-260.107954005044</v>
       </c>
       <c r="K12" s="4" t="n">
         <f aca="false">-K6*Assumptions!K31/100</f>
-        <v>-280.518401484626</v>
+        <v>-267.911192625196</v>
       </c>
       <c r="L12" s="4" t="n">
         <f aca="false">-L6*Assumptions!L31/100</f>
-        <v>-288.933953529164</v>
+        <v>-275.948528403952</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
-        <v>667.128187363</v>
+        <v>599.664203264</v>
       </c>
       <c r="D13" s="0" t="n">
         <f aca="false">D11+D12</f>
-        <v>702.058455483027</v>
+        <v>535.62194030604</v>
       </c>
       <c r="E13" s="0" t="n">
         <f aca="false">E11+E12</f>
-        <v>749.386032482023</v>
+        <v>580.353610455923</v>
       </c>
       <c r="F13" s="0" t="n">
         <f aca="false">F11+F12</f>
-        <v>801.582851272264</v>
+        <v>630.75273978499</v>
       </c>
       <c r="G13" s="0" t="n">
         <f aca="false">G11+G12</f>
-        <v>847.426802012835</v>
+        <v>681.480227077867</v>
       </c>
       <c r="H13" s="0" t="n">
         <f aca="false">H11+H12</f>
-        <v>885.561008103413</v>
+        <v>708.739436160982</v>
       </c>
       <c r="I13" s="0" t="n">
         <f aca="false">I11+I12</f>
-        <v>920.98344842755</v>
+        <v>733.545316426616</v>
       </c>
       <c r="J13" s="0" t="n">
         <f aca="false">J11+J12</f>
-        <v>953.217869122514</v>
+        <v>755.551675919415</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">K11+K12</f>
-        <v>981.814405196189</v>
+        <v>778.218226196997</v>
       </c>
       <c r="L13" s="0" t="n">
         <f aca="false">L11+L12</f>
-        <v>1011.26883735207</v>
+        <v>801.564772982907</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C33</f>
@@ -5112,232 +5349,232 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
-        <v>527.03126801677</v>
+        <v>473.73472057856</v>
       </c>
       <c r="D15" s="0" t="n">
         <f aca="false">D13-MAX(0,D13)*D14/100</f>
-        <v>547.605595276761</v>
+        <v>417.785113438711</v>
       </c>
       <c r="E15" s="0" t="n">
         <f aca="false">E13-MAX(0,E13)*E14/100</f>
-        <v>577.027245011158</v>
+        <v>446.872280051061</v>
       </c>
       <c r="F15" s="0" t="n">
         <f aca="false">F13-MAX(0,F13)*F14/100</f>
-        <v>609.202966966921</v>
+        <v>479.372082236592</v>
       </c>
       <c r="G15" s="0" t="n">
         <f aca="false">G13-MAX(0,G13)*G14/100</f>
-        <v>644.044369529755</v>
+        <v>517.924972579179</v>
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">H13-MAX(0,H13)*H14/100</f>
-        <v>673.026366158594</v>
+        <v>538.641971482346</v>
       </c>
       <c r="I15" s="0" t="n">
         <f aca="false">I13-MAX(0,I13)*I14/100</f>
-        <v>699.947420804938</v>
+        <v>557.494440484228</v>
       </c>
       <c r="J15" s="0" t="n">
         <f aca="false">J13-MAX(0,J13)*J14/100</f>
-        <v>724.44558053311</v>
+        <v>574.219273698755</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">K13-MAX(0,K13)*K14/100</f>
-        <v>746.178947949104</v>
+        <v>591.445851909718</v>
       </c>
       <c r="L15" s="0" t="n">
         <f aca="false">L13-MAX(0,L13)*L14/100</f>
-        <v>768.564316387577</v>
+        <v>609.189227467009</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
-        <v>187.92343306</v>
+        <v>187.39506352</v>
       </c>
       <c r="D16" s="0" t="n">
         <f aca="false">-D12</f>
-        <v>201.289487236392</v>
+        <v>197.84233831124</v>
       </c>
       <c r="E16" s="0" t="n">
         <f aca="false">-E12</f>
-        <v>218.57092614059</v>
+        <v>213.814488062708</v>
       </c>
       <c r="F16" s="0" t="n">
         <f aca="false">-F12</f>
-        <v>230.592327078323</v>
+        <v>224.505212465844</v>
       </c>
       <c r="G16" s="0" t="n">
         <f aca="false">-G12</f>
-        <v>242.121943432239</v>
+        <v>234.607947026807</v>
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">-H12</f>
-        <v>253.017430886689</v>
+        <v>243.992264907879</v>
       </c>
       <c r="I16" s="0" t="n">
         <f aca="false">-I12</f>
-        <v>263.138128122157</v>
+        <v>252.531994179655</v>
       </c>
       <c r="J16" s="0" t="n">
         <f aca="false">-J12</f>
-        <v>272.347962606433</v>
+        <v>260.107954005044</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">-K12</f>
-        <v>280.518401484626</v>
+        <v>267.911192625196</v>
       </c>
       <c r="L16" s="0" t="n">
         <f aca="false">-L12</f>
-        <v>288.933953529164</v>
+        <v>275.948528403952</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C32/100</f>
-        <v>-328.866007855</v>
+        <v>-337.311114336</v>
       </c>
       <c r="D17" s="4" t="n">
         <f aca="false">-D6*Assumptions!D32/100</f>
-        <v>-324.026979453705</v>
+        <v>-328.12875622352</v>
       </c>
       <c r="E17" s="4" t="n">
         <f aca="false">-E6*Assumptions!E32/100</f>
-        <v>-333.060458880899</v>
+        <v>-325.812553238413</v>
       </c>
       <c r="F17" s="4" t="n">
         <f aca="false">-F6*Assumptions!F32/100</f>
-        <v>-340.398197115619</v>
+        <v>-331.412456497198</v>
       </c>
       <c r="G17" s="4" t="n">
         <f aca="false">-G6*Assumptions!G32/100</f>
-        <v>-345.888490617484</v>
+        <v>-335.154210038295</v>
       </c>
       <c r="H17" s="4" t="n">
         <f aca="false">-H6*Assumptions!H32/100</f>
-        <v>-361.453472695271</v>
+        <v>-348.560378439827</v>
       </c>
       <c r="I17" s="4" t="n">
         <f aca="false">-I6*Assumptions!I32/100</f>
-        <v>-363.381224549645</v>
+        <v>-348.734658629047</v>
       </c>
       <c r="J17" s="4" t="n">
         <f aca="false">-J6*Assumptions!J32/100</f>
-        <v>-363.130616808577</v>
+        <v>-346.810605340059</v>
       </c>
       <c r="K17" s="4" t="n">
         <f aca="false">-K6*Assumptions!K32/100</f>
-        <v>-374.024535312834</v>
+        <v>-357.214923500261</v>
       </c>
       <c r="L17" s="4" t="n">
         <f aca="false">-L6*Assumptions!L32/100</f>
-        <v>-385.245271372219</v>
+        <v>-367.931371205269</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$37/100</f>
-        <v>11.80025306</v>
+        <v>11.27188352</v>
       </c>
       <c r="D18" s="4" t="n">
         <f aca="false">(D6-C6)*Assumptions!$B$37/100</f>
-        <v>8.45655448769998</v>
+        <v>5.62185190560002</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">(E6-D6)*Assumptions!$B$37/100</f>
-        <v>11.782799252862</v>
+        <v>10.615930348408</v>
       </c>
       <c r="F18" s="4" t="n">
         <f aca="false">(F6-E6)*Assumptions!$B$37/100</f>
-        <v>11.4489532740309</v>
+        <v>10.1816422887004</v>
       </c>
       <c r="G18" s="4" t="n">
         <f aca="false">(G6-F6)*Assumptions!$B$37/100</f>
-        <v>10.9805870037297</v>
+        <v>9.62165196282185</v>
       </c>
       <c r="H18" s="4" t="n">
         <f aca="false">(H6-G6)*Assumptions!$B$37/100</f>
-        <v>10.3766547185245</v>
+        <v>8.93744560102121</v>
       </c>
       <c r="I18" s="4" t="n">
         <f aca="false">(I6-H6)*Assumptions!$B$37/100</f>
-        <v>9.6387592718739</v>
+        <v>8.13307549692927</v>
       </c>
       <c r="J18" s="4" t="n">
         <f aca="false">(J6-I6)*Assumptions!$B$37/100</f>
-        <v>8.77127093740521</v>
+        <v>7.21519983370443</v>
       </c>
       <c r="K18" s="4" t="n">
         <f aca="false">(K6-J6)*Assumptions!$B$37/100</f>
-        <v>7.78137036018379</v>
+        <v>7.43165582871556</v>
       </c>
       <c r="L18" s="4" t="n">
         <f aca="false">(L6-K6)*Assumptions!$B$37/100</f>
-        <v>8.0148114709893</v>
+        <v>7.65460550357704</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
-        <v>397.88894628177</v>
+        <v>335.09055328256</v>
       </c>
       <c r="D19" s="0" t="n">
         <f aca="false">D15+D16+D17+D18</f>
-        <v>433.324657547149</v>
+        <v>293.120547432031</v>
       </c>
       <c r="E19" s="0" t="n">
         <f aca="false">E15+E16+E17+E18</f>
-        <v>474.320511523711</v>
+        <v>345.490145223764</v>
       </c>
       <c r="F19" s="0" t="n">
         <f aca="false">F15+F16+F17+F18</f>
-        <v>510.846050203655</v>
+        <v>382.646480493939</v>
       </c>
       <c r="G19" s="0" t="n">
         <f aca="false">G15+G16+G17+G18</f>
-        <v>551.258409348239</v>
+        <v>427.000361530512</v>
       </c>
       <c r="H19" s="0" t="n">
         <f aca="false">H15+H16+H17+H18</f>
-        <v>574.966979068537</v>
+        <v>443.011303551419</v>
       </c>
       <c r="I19" s="0" t="n">
         <f aca="false">I15+I16+I17+I18</f>
-        <v>609.343083649323</v>
+        <v>469.424851531765</v>
       </c>
       <c r="J19" s="0" t="n">
         <f aca="false">J15+J16+J17+J18</f>
-        <v>642.434197268372</v>
+        <v>494.731822197445</v>
       </c>
       <c r="K19" s="0" t="n">
         <f aca="false">K15+K16+K17+K18</f>
-        <v>660.454184481079</v>
+        <v>509.573776863368</v>
       </c>
       <c r="L19" s="0" t="n">
         <f aca="false">L15+L16+L17+L18</f>
-        <v>680.267810015512</v>
+        <v>524.860990169269</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -5382,52 +5619,52 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
-        <v>365.035730533734</v>
+        <v>307.422525947303</v>
       </c>
       <c r="D21" s="0" t="n">
         <f aca="false">D19*D20</f>
-        <v>364.720694846519</v>
+        <v>246.713700388882</v>
       </c>
       <c r="E21" s="0" t="n">
         <f aca="false">E19*E20</f>
-        <v>366.262463252723</v>
+        <v>266.781782665689</v>
       </c>
       <c r="F21" s="0" t="n">
         <f aca="false">F19*F20</f>
-        <v>361.896220937346</v>
+        <v>271.076413707273</v>
       </c>
       <c r="G21" s="0" t="n">
         <f aca="false">G19*G20</f>
-        <v>358.280142196322</v>
+        <v>277.520936919421</v>
       </c>
       <c r="H21" s="0" t="n">
         <f aca="false">H19*H20</f>
-        <v>342.834023653015</v>
+        <v>264.153165745882</v>
       </c>
       <c r="I21" s="0" t="n">
         <f aca="false">I19*I20</f>
-        <v>333.331533614606</v>
+        <v>256.791469168366</v>
       </c>
       <c r="J21" s="0" t="n">
         <f aca="false">J19*J20</f>
-        <v>322.416060517639</v>
+        <v>248.289219041961</v>
       </c>
       <c r="K21" s="0" t="n">
         <f aca="false">K19*K20</f>
-        <v>304.091453632873</v>
+        <v>234.621922580936</v>
       </c>
       <c r="L21" s="0" t="n">
         <f aca="false">L19*L20</f>
-        <v>287.352474533815</v>
+        <v>221.706954365471</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C30</f>
@@ -5472,7 +5709,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -5517,12 +5754,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$34</f>
@@ -5531,7 +5768,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -5540,7 +5777,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -5549,124 +5786,124 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
-        <v>3406.22079771859</v>
+        <v>2595.07809053118</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
-        <v>680.267810015512</v>
+        <v>524.860990169269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
-        <v>10727.3000810138</v>
+        <v>8276.65407574617</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
-        <v>10884.2849602482</v>
+        <v>8397.77584270831</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
-        <v>10727.3000810138</v>
+        <v>8276.65407574617</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
-        <v>4531.32748303324</v>
+        <v>3496.14812653243</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
-        <v>7937.54828075183</v>
+        <v>6091.22621706361</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
-        <v>8047.65228075183</v>
+        <v>6186.80421706361</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>85.2415239990661</v>
+        <v>66.0517606929261</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
-        <v>0.364082637207011</v>
+        <v>0.329009269475374</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
-        <v>254.46313187232</v>
+        <v>211.687555451667</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
-        <v>320.769346310413</v>
+        <v>262.588421007497</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>91.3344429502655</v>
+        <v>71.1152413204661</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -5675,20 +5912,20 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
-        <v>5578.19604212719</v>
+        <v>4303.86011938801</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>43.2599800459514</v>
+        <v>33.4700885866364</v>
       </c>
     </row>
   </sheetData>
@@ -5715,50 +5952,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -5806,15 +6043,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C41</f>
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">Assumptions!D41</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">Assumptions!E41</f>
@@ -5822,23 +6059,23 @@
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">Assumptions!F41</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">Assumptions!G41</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="4" t="n">
         <f aca="false">Assumptions!H41</f>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="I5" s="4" t="n">
         <f aca="false">Assumptions!I41</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
         <f aca="false">Assumptions!J41</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K5" s="4" t="n">
         <f aca="false">Assumptions!K41</f>
@@ -5851,370 +6088,370 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>8806.159</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">B6*(1+C5/100)</f>
-        <v>9422.59013</v>
+        <v>9387.365494</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">C6*(1+D5/100)</f>
-        <v>9987.9455378</v>
+        <v>9856.7337687</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">D6*(1+E5/100)</f>
-        <v>10786.981180824</v>
+        <v>10645.272470196</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">E6*(1+F5/100)</f>
-        <v>11596.0047693858</v>
+        <v>11390.4415431097</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">F6*(1+G5/100)</f>
-        <v>12407.7251032428</v>
+        <v>12073.8680356963</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">G6*(1+H5/100)</f>
-        <v>13214.2272349536</v>
+        <v>12737.9307776596</v>
       </c>
       <c r="I6" s="0" t="n">
         <f aca="false">H6*(1+I5/100)</f>
-        <v>14007.0808690508</v>
+        <v>13374.8273165426</v>
       </c>
       <c r="J6" s="0" t="n">
         <f aca="false">I6*(1+J5/100)</f>
-        <v>14707.4349125033</v>
+        <v>13976.694545787</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">J6*(1+K5/100)</f>
-        <v>15295.7323090035</v>
+        <v>14535.7623276185</v>
       </c>
       <c r="L6" s="0" t="n">
         <f aca="false">K6*(1+L5/100)</f>
-        <v>15831.0829398186</v>
+        <v>15044.5140090851</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C42</f>
-        <v>9.5</v>
+        <v>8.8</v>
       </c>
       <c r="D7" s="4" t="n">
         <f aca="false">Assumptions!D42</f>
-        <v>9.8</v>
+        <v>8.3</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">Assumptions!E42</f>
-        <v>10.1</v>
+        <v>8.8</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">Assumptions!F42</f>
-        <v>10.4</v>
+        <v>9.2</v>
       </c>
       <c r="G7" s="4" t="n">
         <f aca="false">Assumptions!G42</f>
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="H7" s="4" t="n">
         <f aca="false">Assumptions!H42</f>
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="I7" s="4" t="n">
         <f aca="false">Assumptions!I42</f>
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="J7" s="4" t="n">
         <f aca="false">Assumptions!J42</f>
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="K7" s="4" t="n">
         <f aca="false">Assumptions!K42</f>
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="L7" s="4" t="n">
         <f aca="false">Assumptions!L42</f>
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">C6*C7/100</f>
-        <v>895.14606235</v>
+        <v>826.088163472</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">D6*D7/100</f>
-        <v>978.8186627044</v>
+        <v>818.1089028021</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">E6*E7/100</f>
-        <v>1089.48509926322</v>
+        <v>936.783977377248</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">F6*F7/100</f>
-        <v>1205.98449601612</v>
+        <v>1047.92062196609</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">G6*G7/100</f>
-        <v>1315.21886094374</v>
+        <v>1147.01746339115</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">H6*H7/100</f>
-        <v>1427.13654137499</v>
+        <v>1222.84135465532</v>
       </c>
       <c r="I8" s="0" t="n">
         <f aca="false">I6*I7/100</f>
-        <v>1512.76473385749</v>
+        <v>1283.98342238809</v>
       </c>
       <c r="J8" s="0" t="n">
         <f aca="false">J6*J7/100</f>
-        <v>1588.40297055036</v>
+        <v>1341.76267639555</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">K6*K7/100</f>
-        <v>1651.93908937238</v>
+        <v>1395.43318345137</v>
       </c>
       <c r="L8" s="0" t="n">
         <f aca="false">L6*L7/100</f>
-        <v>1709.75695750041</v>
+        <v>1444.27334487217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="4" t="n">
         <f aca="false">Assumptions!D43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">Assumptions!E43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">Assumptions!F43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="4" t="n">
         <f aca="false">Assumptions!G43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="4" t="n">
         <f aca="false">Assumptions!H43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="4" t="n">
         <f aca="false">Assumptions!I43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="4" t="n">
         <f aca="false">Assumptions!J43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="4" t="n">
         <f aca="false">Assumptions!K43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L9" s="4" t="n">
         <f aca="false">Assumptions!L43</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
-        <v>-32.979065455</v>
+        <v>-28.162096482</v>
       </c>
       <c r="D10" s="0" t="n">
         <f aca="false">-D6*D9/100</f>
-        <v>-34.9578093823</v>
+        <v>-29.5702013061</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">-E6*E9/100</f>
-        <v>-37.754434132884</v>
+        <v>-31.935817410588</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">-F6*F9/100</f>
-        <v>-40.5860166928503</v>
+        <v>-34.1713246293292</v>
       </c>
       <c r="G10" s="0" t="n">
         <f aca="false">-G6*G9/100</f>
-        <v>-43.4270378613498</v>
+        <v>-36.2216041070889</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">-H6*H9/100</f>
-        <v>-46.2497953223376</v>
+        <v>-38.2137923329788</v>
       </c>
       <c r="I10" s="0" t="n">
         <f aca="false">-I6*I9/100</f>
-        <v>-49.0247830416778</v>
+        <v>-40.1244819496278</v>
       </c>
       <c r="J10" s="0" t="n">
         <f aca="false">-J6*J9/100</f>
-        <v>-51.4760221937617</v>
+        <v>-41.930083637361</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">-K6*K9/100</f>
-        <v>-53.5350630815122</v>
+        <v>-43.6072869828554</v>
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">-L6*L9/100</f>
-        <v>-55.4087902893651</v>
+        <v>-45.1335420272554</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
-        <v>862.166996895</v>
+        <v>797.92606699</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">D8+D10+D24</f>
-        <v>943.8608533221</v>
+        <v>788.538701496</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">E8+E10+E24</f>
-        <v>1051.73066513034</v>
+        <v>904.84815996666</v>
       </c>
       <c r="F11" s="0" t="n">
         <f aca="false">F8+F10+F24</f>
-        <v>1165.39847932327</v>
+        <v>1013.74929733677</v>
       </c>
       <c r="G11" s="0" t="n">
         <f aca="false">G8+G10+G24</f>
-        <v>1271.79182308239</v>
+        <v>1110.79585928406</v>
       </c>
       <c r="H11" s="0" t="n">
         <f aca="false">H8+H10+H24</f>
-        <v>1380.88674605265</v>
+        <v>1184.62756232234</v>
       </c>
       <c r="I11" s="0" t="n">
         <f aca="false">I8+I10+I24</f>
-        <v>1463.73995081581</v>
+        <v>1243.85894043846</v>
       </c>
       <c r="J11" s="0" t="n">
         <f aca="false">J8+J10+J24</f>
-        <v>1536.9269483566</v>
+        <v>1299.83259275819</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">K8+K10+K24</f>
-        <v>1598.40402629086</v>
+        <v>1351.82589646852</v>
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">L8+L10+L24</f>
-        <v>1654.34816721104</v>
+        <v>1399.13980284492</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C45/100</f>
-        <v>-188.4518026</v>
+        <v>-187.74730988</v>
       </c>
       <c r="D12" s="4" t="n">
         <f aca="false">-D6*Assumptions!D45/100</f>
-        <v>-204.7528835249</v>
+        <v>-202.06304225835</v>
       </c>
       <c r="E12" s="4" t="n">
         <f aca="false">-E6*Assumptions!E45/100</f>
-        <v>-226.526604797304</v>
+        <v>-223.550721874116</v>
       </c>
       <c r="F12" s="4" t="n">
         <f aca="false">-F6*Assumptions!F45/100</f>
-        <v>-243.516100157102</v>
+        <v>-239.199272405304</v>
       </c>
       <c r="G12" s="4" t="n">
         <f aca="false">-G6*Assumptions!G45/100</f>
-        <v>-260.562227168099</v>
+        <v>-253.551228749622</v>
       </c>
       <c r="H12" s="4" t="n">
         <f aca="false">-H6*Assumptions!H45/100</f>
-        <v>-277.498771934025</v>
+        <v>-267.496546330852</v>
       </c>
       <c r="I12" s="4" t="n">
         <f aca="false">-I6*Assumptions!I45/100</f>
-        <v>-294.148698250067</v>
+        <v>-280.871373647394</v>
       </c>
       <c r="J12" s="4" t="n">
         <f aca="false">-J6*Assumptions!J45/100</f>
-        <v>-308.85613316257</v>
+        <v>-293.510585461527</v>
       </c>
       <c r="K12" s="4" t="n">
         <f aca="false">-K6*Assumptions!K45/100</f>
-        <v>-321.210378489073</v>
+        <v>-305.251008879988</v>
       </c>
       <c r="L12" s="4" t="n">
         <f aca="false">-L6*Assumptions!L45/100</f>
-        <v>-332.452741736191</v>
+        <v>-315.934794190788</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
-        <v>673.715194295</v>
+        <v>610.17875711</v>
       </c>
       <c r="D13" s="0" t="n">
         <f aca="false">D11+D12</f>
-        <v>739.1079697972</v>
+        <v>586.47565923765</v>
       </c>
       <c r="E13" s="0" t="n">
         <f aca="false">E11+E12</f>
-        <v>825.204060333036</v>
+        <v>681.297438092544</v>
       </c>
       <c r="F13" s="0" t="n">
         <f aca="false">F11+F12</f>
-        <v>921.882379166171</v>
+        <v>774.550024931461</v>
       </c>
       <c r="G13" s="0" t="n">
         <f aca="false">G11+G12</f>
-        <v>1011.22959591429</v>
+        <v>857.244630534438</v>
       </c>
       <c r="H13" s="0" t="n">
         <f aca="false">H11+H12</f>
-        <v>1103.38797411863</v>
+        <v>917.131015991492</v>
       </c>
       <c r="I13" s="0" t="n">
         <f aca="false">I11+I12</f>
-        <v>1169.59125256574</v>
+        <v>962.987566791066</v>
       </c>
       <c r="J13" s="0" t="n">
         <f aca="false">J11+J12</f>
-        <v>1228.07081519403</v>
+        <v>1006.32200729666</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">K11+K12</f>
-        <v>1277.19364780179</v>
+        <v>1046.57488758853</v>
       </c>
       <c r="L13" s="0" t="n">
         <f aca="false">L11+L12</f>
-        <v>1321.89542547485</v>
+        <v>1083.20500865413</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C47</f>
@@ -6259,232 +6496,232 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
-        <v>532.23500349305</v>
+        <v>482.0412181169</v>
       </c>
       <c r="D15" s="0" t="n">
         <f aca="false">D13-MAX(0,D13)*D14/100</f>
-        <v>576.504216441816</v>
+        <v>457.451014205367</v>
       </c>
       <c r="E15" s="0" t="n">
         <f aca="false">E13-MAX(0,E13)*E14/100</f>
-        <v>635.407126456438</v>
+        <v>524.599027331259</v>
       </c>
       <c r="F15" s="0" t="n">
         <f aca="false">F13-MAX(0,F13)*F14/100</f>
-        <v>700.63060816629</v>
+        <v>588.65801894791</v>
       </c>
       <c r="G15" s="0" t="n">
         <f aca="false">G13-MAX(0,G13)*G14/100</f>
-        <v>768.53449289486</v>
+        <v>651.505919206173</v>
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">H13-MAX(0,H13)*H14/100</f>
-        <v>838.574860330155</v>
+        <v>697.019572153534</v>
       </c>
       <c r="I15" s="0" t="n">
         <f aca="false">I13-MAX(0,I13)*I14/100</f>
-        <v>888.889351949965</v>
+        <v>731.87055076121</v>
       </c>
       <c r="J15" s="0" t="n">
         <f aca="false">J13-MAX(0,J13)*J14/100</f>
-        <v>933.333819547463</v>
+        <v>764.804725545465</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">K13-MAX(0,K13)*K14/100</f>
-        <v>970.667172329361</v>
+        <v>795.396914567283</v>
       </c>
       <c r="L15" s="0" t="n">
         <f aca="false">L13-MAX(0,L13)*L14/100</f>
-        <v>1004.64052336089</v>
+        <v>823.235806577138</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
-        <v>188.4518026</v>
+        <v>187.74730988</v>
       </c>
       <c r="D16" s="0" t="n">
         <f aca="false">-D12</f>
-        <v>204.7528835249</v>
+        <v>202.06304225835</v>
       </c>
       <c r="E16" s="0" t="n">
         <f aca="false">-E12</f>
-        <v>226.526604797304</v>
+        <v>223.550721874116</v>
       </c>
       <c r="F16" s="0" t="n">
         <f aca="false">-F12</f>
-        <v>243.516100157102</v>
+        <v>239.199272405304</v>
       </c>
       <c r="G16" s="0" t="n">
         <f aca="false">-G12</f>
-        <v>260.562227168099</v>
+        <v>253.551228749622</v>
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">-H12</f>
-        <v>277.498771934025</v>
+        <v>267.496546330852</v>
       </c>
       <c r="I16" s="0" t="n">
         <f aca="false">-I12</f>
-        <v>294.148698250067</v>
+        <v>280.871373647394</v>
       </c>
       <c r="J16" s="0" t="n">
         <f aca="false">-J12</f>
-        <v>308.85613316257</v>
+        <v>293.510585461527</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">-K12</f>
-        <v>321.210378489073</v>
+        <v>305.251008879988</v>
       </c>
       <c r="L16" s="0" t="n">
         <f aca="false">-L12</f>
-        <v>332.452741736191</v>
+        <v>315.934794190788</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C46/100</f>
-        <v>-329.79065455</v>
+        <v>-337.945157784</v>
       </c>
       <c r="D17" s="4" t="n">
         <f aca="false">-D6*Assumptions!D46/100</f>
-        <v>-339.5901482852</v>
+        <v>-344.9856819045</v>
       </c>
       <c r="E17" s="4" t="n">
         <f aca="false">-E6*Assumptions!E46/100</f>
-        <v>-355.970378967192</v>
+        <v>-361.939263986664</v>
       </c>
       <c r="F17" s="4" t="n">
         <f aca="false">-F6*Assumptions!F46/100</f>
-        <v>-371.072152620346</v>
+        <v>-375.884570922621</v>
       </c>
       <c r="G17" s="4" t="n">
         <f aca="false">-G6*Assumptions!G46/100</f>
-        <v>-384.639478200527</v>
+        <v>-386.363777142282</v>
       </c>
       <c r="H17" s="4" t="n">
         <f aca="false">-H6*Assumptions!H46/100</f>
-        <v>-396.426817048608</v>
+        <v>-394.875854107448</v>
       </c>
       <c r="I17" s="4" t="n">
         <f aca="false">-I6*Assumptions!I46/100</f>
-        <v>-420.212426071524</v>
+        <v>-401.244819496278</v>
       </c>
       <c r="J17" s="4" t="n">
         <f aca="false">-J6*Assumptions!J46/100</f>
-        <v>-426.515612462597</v>
+        <v>-419.30083637361</v>
       </c>
       <c r="K17" s="4" t="n">
         <f aca="false">-K6*Assumptions!K46/100</f>
-        <v>-443.576236961101</v>
+        <v>-421.537107500936</v>
       </c>
       <c r="L17" s="4" t="n">
         <f aca="false">-L6*Assumptions!L46/100</f>
-        <v>-459.10140525474</v>
+        <v>-436.290906263469</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$51/100</f>
-        <v>12.3286226</v>
+        <v>11.62412988</v>
       </c>
       <c r="D18" s="4" t="n">
         <f aca="false">(D6-C6)*Assumptions!$B$51/100</f>
-        <v>11.307108156</v>
+        <v>9.387365494</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">(E6-D6)*Assumptions!$B$51/100</f>
-        <v>15.98071286048</v>
+        <v>15.77077402992</v>
       </c>
       <c r="F18" s="4" t="n">
         <f aca="false">(F6-E6)*Assumptions!$B$51/100</f>
-        <v>16.180471771236</v>
+        <v>14.9033814582744</v>
       </c>
       <c r="G18" s="4" t="n">
         <f aca="false">(G6-F6)*Assumptions!$B$51/100</f>
-        <v>16.2344066771401</v>
+        <v>13.6685298517317</v>
       </c>
       <c r="H18" s="4" t="n">
         <f aca="false">(H6-G6)*Assumptions!$B$51/100</f>
-        <v>16.1300426342156</v>
+        <v>13.2812548392659</v>
       </c>
       <c r="I18" s="4" t="n">
         <f aca="false">(I6-H6)*Assumptions!$B$51/100</f>
-        <v>15.8570726819443</v>
+        <v>12.7379307776596</v>
       </c>
       <c r="J18" s="4" t="n">
         <f aca="false">(J6-I6)*Assumptions!$B$51/100</f>
-        <v>14.0070808690508</v>
+        <v>12.0373445848883</v>
       </c>
       <c r="K18" s="4" t="n">
         <f aca="false">(K6-J6)*Assumptions!$B$51/100</f>
-        <v>11.7659479300027</v>
+        <v>11.1813556366296</v>
       </c>
       <c r="L18" s="4" t="n">
         <f aca="false">(L6-K6)*Assumptions!$B$51/100</f>
-        <v>10.7070126163024</v>
+        <v>10.1750336293329</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
-        <v>403.22477414305</v>
+        <v>343.4675000929</v>
       </c>
       <c r="D19" s="0" t="n">
         <f aca="false">D15+D16+D17+D18</f>
-        <v>452.974059837516</v>
+        <v>323.915740053217</v>
       </c>
       <c r="E19" s="0" t="n">
         <f aca="false">E15+E16+E17+E18</f>
-        <v>521.94406514703</v>
+        <v>401.981259248631</v>
       </c>
       <c r="F19" s="0" t="n">
         <f aca="false">F15+F16+F17+F18</f>
-        <v>589.255027474282</v>
+        <v>466.876101888868</v>
       </c>
       <c r="G19" s="0" t="n">
         <f aca="false">G15+G16+G17+G18</f>
-        <v>660.691648539572</v>
+        <v>532.361900665245</v>
       </c>
       <c r="H19" s="0" t="n">
         <f aca="false">H15+H16+H17+H18</f>
-        <v>735.776857849788</v>
+        <v>582.921519216203</v>
       </c>
       <c r="I19" s="0" t="n">
         <f aca="false">I15+I16+I17+I18</f>
-        <v>778.682696810452</v>
+        <v>624.235035689986</v>
       </c>
       <c r="J19" s="0" t="n">
         <f aca="false">J15+J16+J17+J18</f>
-        <v>829.681421116487</v>
+        <v>651.05181921827</v>
       </c>
       <c r="K19" s="0" t="n">
         <f aca="false">K15+K16+K17+K18</f>
-        <v>860.067261787336</v>
+        <v>690.292171582965</v>
       </c>
       <c r="L19" s="0" t="n">
         <f aca="false">L15+L16+L17+L18</f>
-        <v>888.698872458642</v>
+        <v>713.05472813379</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -6529,52 +6766,52 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
-        <v>369.930985452339</v>
+        <v>315.107798250367</v>
       </c>
       <c r="D21" s="0" t="n">
         <f aca="false">D19*D20</f>
-        <v>381.259203633967</v>
+        <v>272.633397906924</v>
       </c>
       <c r="E21" s="0" t="n">
         <f aca="false">E19*E20</f>
-        <v>403.036584622452</v>
+        <v>310.403287685937</v>
       </c>
       <c r="F21" s="0" t="n">
         <f aca="false">F19*F20</f>
-        <v>417.443117209697</v>
+        <v>330.746801021917</v>
       </c>
       <c r="G21" s="0" t="n">
         <f aca="false">G19*G20</f>
-        <v>429.404239051063</v>
+        <v>345.998708111785</v>
       </c>
       <c r="H21" s="0" t="n">
         <f aca="false">H19*H20</f>
-        <v>438.719700209682</v>
+        <v>347.577056043417</v>
       </c>
       <c r="I21" s="0" t="n">
         <f aca="false">I19*I20</f>
-        <v>425.966101022263</v>
+        <v>341.477941353413</v>
       </c>
       <c r="J21" s="0" t="n">
         <f aca="false">J19*J20</f>
-        <v>416.389128129346</v>
+        <v>326.740954385261</v>
       </c>
       <c r="K21" s="0" t="n">
         <f aca="false">K19*K20</f>
-        <v>395.998859579408</v>
+        <v>317.82969177943</v>
       </c>
       <c r="L21" s="0" t="n">
         <f aca="false">L19*L20</f>
-        <v>375.396007802544</v>
+        <v>301.20202307178</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C44</f>
@@ -6619,7 +6856,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -6664,12 +6901,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$48</f>
@@ -6678,7 +6915,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$49</f>
@@ -6687,7 +6924,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$50</f>
@@ -6696,124 +6933,124 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
-        <v>4053.54392671276</v>
+        <v>3209.71765961023</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
-        <v>888.698872458642</v>
+        <v>713.05472813379</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
-        <v>15255.99731054</v>
+        <v>12240.7728329634</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
-        <v>14219.1819593383</v>
+        <v>11408.8756501406</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
-        <v>14219.1819593383</v>
+        <v>11408.8756501406</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
-        <v>6006.3361248407</v>
+        <v>4819.23236914848</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
-        <v>10059.8800515535</v>
+        <v>8028.95002875872</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
-        <v>10169.9840515535</v>
+        <v>8124.52802875872</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>107.721470729303</v>
+        <v>86.7393507650451</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
-        <v>0.723819342763685</v>
+        <v>0.745258566701109</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
-        <v>274.093273599411</v>
+        <v>228.056427251231</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
-        <v>401.790499495034</v>
+        <v>327.280713049454</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>114.880498089693</v>
+        <v>92.6682592302372</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -6822,20 +7059,20 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
-        <v>7627.99865527001</v>
+        <v>6120.3864164817</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>53.421906557143</v>
+        <v>42.9180246014283</v>
       </c>
     </row>
   </sheetData>
@@ -6862,65 +7099,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">DCF_Bear!$B$38</f>
-        <v>59.5245462244735</v>
+        <v>48.6288163974741</v>
       </c>
       <c r="C4" s="0" t="n">
         <f aca="false">B4/Assumptions!$B$2-1</f>
-        <v>-0.0474548531849344</v>
+        <v>-0.0215529899904607</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">Assumptions!$B$24</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E4" s="4" t="n">
         <f aca="false">DCF_Bear!$B$43</f>
-        <v>64.611816813273</v>
+        <v>52.981381015341</v>
       </c>
       <c r="F4" s="4" t="n">
         <f aca="false">DCF_Bear!$B$47</f>
-        <v>32.9918439767351</v>
+        <v>26.898179438958</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">DCF_Base!$B$38</f>
-        <v>85.2415239990661</v>
+        <v>66.0517606929261</v>
       </c>
       <c r="C5" s="0" t="n">
         <f aca="false">B5/Assumptions!$B$2-1</f>
-        <v>0.364082637207011</v>
+        <v>0.329009269475374</v>
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">Assumptions!$B$38</f>
@@ -6928,98 +7165,98 @@
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">DCF_Base!$B$43</f>
-        <v>91.3344429502655</v>
+        <v>71.1152413204661</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">DCF_Base!$B$47</f>
-        <v>43.2599800459514</v>
+        <v>33.4700885866364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">DCF_Bull!$B$38</f>
-        <v>107.721470729303</v>
+        <v>86.7393507650451</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">B6/Assumptions!$B$2-1</f>
-        <v>0.723819342763685</v>
+        <v>0.745258566701109</v>
       </c>
       <c r="D6" s="4" t="n">
         <f aca="false">Assumptions!$B$52</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="4" t="n">
         <f aca="false">DCF_Bull!$B$43</f>
-        <v>114.880498089693</v>
+        <v>92.6682592302372</v>
       </c>
       <c r="F6" s="4" t="n">
         <f aca="false">DCF_Bull!$B$47</f>
-        <v>53.421906557143</v>
+        <v>42.9180246014283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">SUMPRODUCT(B4:B6,D4:D6)</f>
-        <v>84.4322662379771</v>
+        <v>64.9623954187143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">SUMPRODUCT(E4:E6,D4:D6)</f>
-        <v>90.5403002008742</v>
+        <v>69.9856868108828</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">1-Assumptions!$B$2/B8</f>
-        <v>0.259880105268424</v>
+        <v>0.234942004837425</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">IF(ABS(B9-B8)&gt;0.01*ABS(B8),(Assumptions!$B$2-B8)/(B9-B8)*100,"n/a")</f>
-        <v>-359.236153093844</v>
+        <v>-303.832571658274</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">SUMPRODUCT(F4:F6,D4:D6)</f>
-        <v>43.2334276564452</v>
+        <v>33.3881030452912</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$15/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$15&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$15-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$15/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>85.2415239990661</v>
+        <v>66.0517606929261</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>9</v>
@@ -7027,11 +7264,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$16/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$16&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$16-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$16/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>73.52202406866</v>
+        <v>56.9499306170815</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>10</v>
@@ -7039,11 +7276,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$17/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$17&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$17-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$17/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>64.5823088052167</v>
+        <v>50.0094130346228</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>11</v>
@@ -7051,11 +7288,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$18/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$18&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$18-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$18/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>57.5432735511123</v>
+        <v>44.5465694284693</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>12</v>
@@ -7063,11 +7300,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$19/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$19&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$19-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$19/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>43.2599800459514</v>
+        <v>33.4700885866364</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>15</v>
@@ -7075,7 +7312,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7101,23 +7338,23 @@
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$23/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$23&gt;$B$22,DCF_Base!$L$19*(1+$B$22/100)/(($A$23-$B$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$23/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>99.6183130179187</v>
+        <v>77.2064274397013</v>
       </c>
       <c r="C23" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$23/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$23&gt;$C$22,DCF_Base!$L$19*(1+$C$22/100)/(($A$23-$C$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$23/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>99.6183130179187</v>
+        <v>77.2064274397013</v>
       </c>
       <c r="D23" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$23/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$23&gt;$D$22,DCF_Base!$L$19*(1+$D$22/100)/(($A$23-$D$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$23/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>99.6183130179187</v>
+        <v>77.2064274397013</v>
       </c>
       <c r="E23" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$23/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$23&gt;$E$22,DCF_Base!$L$19*(1+$E$22/100)/(($A$23-$E$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$23/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>99.6183130179187</v>
+        <v>77.2064274397013</v>
       </c>
       <c r="F23" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$23/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$23&gt;$F$22,DCF_Base!$L$19*(1+$F$22/100)/(($A$23-$F$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$23/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>99.6183130179187</v>
+        <v>77.2064274397013</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7126,23 +7363,23 @@
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$24/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$24&gt;$B$22,DCF_Base!$L$19*(1+$B$22/100)/(($A$24-$B$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$24/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>91.1768580765513</v>
+        <v>70.6548741495711</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$24/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$24&gt;$C$22,DCF_Base!$L$19*(1+$C$22/100)/(($A$24-$C$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$24/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>92.4605210675677</v>
+        <v>71.6531519615515</v>
       </c>
       <c r="D24" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$24/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$24&gt;$D$22,DCF_Base!$L$19*(1+$D$22/100)/(($A$24-$D$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$24/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>92.4605210675677</v>
+        <v>71.6531519615515</v>
       </c>
       <c r="E24" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$24/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$24&gt;$E$22,DCF_Base!$L$19*(1+$E$22/100)/(($A$24-$E$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$24/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>92.4605210675677</v>
+        <v>71.6531519615515</v>
       </c>
       <c r="F24" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$24/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$24&gt;$F$22,DCF_Base!$L$19*(1+$F$22/100)/(($A$24-$F$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$24/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>92.4605210675677</v>
+        <v>71.6531519615515</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7151,23 +7388,23 @@
       </c>
       <c r="B25" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$25/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$25&gt;$B$22,DCF_Base!$L$19*(1+$B$22/100)/(($A$25-$B$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$25/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>78.4361997642505</v>
+        <v>60.7594026250425</v>
       </c>
       <c r="C25" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$25/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$25&gt;$C$22,DCF_Base!$L$19*(1+$C$22/100)/(($A$25-$C$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$25/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>81.5958145875578</v>
+        <v>63.2165688708456</v>
       </c>
       <c r="D25" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$25/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$25&gt;$D$22,DCF_Base!$L$19*(1+$D$22/100)/(($A$25-$D$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$25/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>85.2415239990661</v>
+        <v>66.0517606929261</v>
       </c>
       <c r="E25" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$25/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$25&gt;$E$22,DCF_Base!$L$19*(1+$E$22/100)/(($A$25-$E$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$25/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>85.9439083810999</v>
+        <v>66.5979903100242</v>
       </c>
       <c r="F25" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$25/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$25&gt;$F$22,DCF_Base!$L$19*(1+$F$22/100)/(($A$25-$F$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$25/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>85.9439083810999</v>
+        <v>66.5979903100242</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7176,23 +7413,23 @@
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$26/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$26&gt;$B$22,DCF_Base!$L$19*(1+$B$22/100)/(($A$26-$B$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$26/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>68.7285810662688</v>
+        <v>53.2221704294241</v>
       </c>
       <c r="C26" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$26/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$26&gt;$C$22,DCF_Base!$L$19*(1+$C$22/100)/(($A$26-$C$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$26/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>70.9755074736396</v>
+        <v>54.9695580173885</v>
       </c>
       <c r="D26" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$26/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$26&gt;$D$22,DCF_Base!$L$19*(1+$D$22/100)/(($A$26-$D$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$26/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>73.52202406866</v>
+        <v>56.9499306170815</v>
       </c>
       <c r="E26" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$26/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$26&gt;$E$22,DCF_Base!$L$19*(1+$E$22/100)/(($A$26-$E$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$26/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>76.4323287486832</v>
+        <v>59.2132135881592</v>
       </c>
       <c r="F26" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$26/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$26&gt;$F$22,DCF_Base!$L$19*(1+$F$22/100)/(($A$26-$F$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$26/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>79.7903726102485</v>
+        <v>61.8246939394027</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7201,23 +7438,23 @@
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$27/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$27&gt;$B$22,DCF_Base!$L$19*(1+$B$22/100)/(($A$27-$B$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$27/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>61.0940188040844</v>
+        <v>47.296642989639</v>
       </c>
       <c r="C27" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$27/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$27&gt;$C$22,DCF_Base!$L$19*(1+$C$22/100)/(($A$27-$C$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$27/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>62.7412668601746</v>
+        <v>48.5776732886591</v>
       </c>
       <c r="D27" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$27/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$27&gt;$D$22,DCF_Base!$L$19*(1+$D$22/100)/(($A$27-$D$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$27/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>64.5823088052167</v>
+        <v>50.0094130346228</v>
       </c>
       <c r="E27" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$27/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$27&gt;$E$22,DCF_Base!$L$19*(1+$E$22/100)/(($A$27-$E$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$27/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>66.653480993389</v>
+        <v>51.620120248832</v>
       </c>
       <c r="F27" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$A$27/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($A$27&gt;$F$22,DCF_Base!$L$19*(1+$F$22/100)/(($A$27-$F$22)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$A$27/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
-        <v>69.0008094733176</v>
+        <v>53.4455884249357</v>
       </c>
     </row>
   </sheetData>
